--- a/runs/RELX/2026-10-14/bear/scratch/g_beta_5ym/out/dcf.xlsx
+++ b/runs/RELX/2026-10-14/bear/scratch/g_beta_5ym/out/dcf.xlsx
@@ -599,7 +599,7 @@
         </is>
       </c>
       <c r="B11" s="2" t="n">
-        <v>0.05</v>
+        <v>0.042</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1366,7 +1366,7 @@
         <v/>
       </c>
       <c r="I15" s="4" t="n">
-        <v>2277.457431452643</v>
+        <v>2302.899123403444</v>
       </c>
     </row>
     <row r="16">
@@ -1392,7 +1392,7 @@
         <v/>
       </c>
       <c r="C17" s="6" t="n">
-        <v>0.07341500000000001</v>
+        <v>0.0703886</v>
       </c>
     </row>
     <row r="18">
@@ -1420,7 +1420,7 @@
         <v/>
       </c>
       <c r="C19" s="6" t="n">
-        <v>0.07009039534000001</v>
+        <v>0.06745191929199999</v>
       </c>
     </row>
     <row r="20">
@@ -1434,7 +1434,7 @@
         <v/>
       </c>
       <c r="C20" s="4" t="n">
-        <v>11804.04901710254</v>
+        <v>11876.22058033421</v>
       </c>
     </row>
     <row r="21">
@@ -1462,7 +1462,7 @@
         <v/>
       </c>
       <c r="C22" s="4" t="n">
-        <v>57481.50927399337</v>
+        <v>60677.66208899429</v>
       </c>
     </row>
     <row r="23">
@@ -1476,7 +1476,7 @@
         <v/>
       </c>
       <c r="C23" s="4" t="n">
-        <v>42377.57152648779</v>
+        <v>45233.62446512853</v>
       </c>
     </row>
     <row r="24">
@@ -1490,7 +1490,7 @@
         <v/>
       </c>
       <c r="C24" s="4" t="n">
-        <v>54181.62054359032</v>
+        <v>57109.84504546275</v>
       </c>
     </row>
     <row r="25">
@@ -1518,7 +1518,7 @@
         <v/>
       </c>
       <c r="C26" s="4" t="n">
-        <v>47184.62054359032</v>
+        <v>50112.84504546275</v>
       </c>
     </row>
     <row r="27">
@@ -1532,7 +1532,7 @@
         <v/>
       </c>
       <c r="C27" s="4" t="n">
-        <v>46604.77054158231</v>
+        <v>49583.0779697424</v>
       </c>
     </row>
     <row r="28">
@@ -1546,7 +1546,7 @@
         <v/>
       </c>
       <c r="C28" s="4" t="n">
-        <v>26.72667768004411</v>
+        <v>28.43466297295514</v>
       </c>
     </row>
     <row r="29">
@@ -1560,7 +1560,7 @@
         <v/>
       </c>
       <c r="C29" s="4" t="n">
-        <v>2672.667768004411</v>
+        <v>2843.466297295514</v>
       </c>
     </row>
     <row r="30">
@@ -1574,7 +1574,7 @@
         <v/>
       </c>
       <c r="C30" s="6" t="n">
-        <v>-0.0354861898</v>
+        <v>0.0261516771</v>
       </c>
     </row>
   </sheetData>
